--- a/verification/cases/roundtrip/pivot/init.xlsx
+++ b/verification/cases/roundtrip/pivot/init.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25427"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\java\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frl\AppData\Local\Temp\xlsx-export-inits-3946636136\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42D3A486-8E76-4FCE-8CF9-F5A003CEC452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{63BEE26E-B140-43BC-8D65-503EA77E7FA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   <calcPr calcId="162913"/>
   <pivotCaches>
     <pivotCache cacheId="0" r:id="rId4"/>
-    <pivotCache cacheId="2" r:id="rId5"/>
+    <pivotCache cacheId="1" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -122,21 +122,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
-      <numFmt numFmtId="21" formatCode="dd/\ mmm"/>
+      <numFmt numFmtId="164" formatCode="dd/\ mmm"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -321,7 +320,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{06C3F5B0-9C80-45BC-B17E-6DD08102FBEF}" name="PivotTable1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{06C3F5B0-9C80-45BC-B17E-6DD08102FBEF}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Werte" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" showAll="0">
@@ -653,9 +652,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -675,7 +674,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -695,7 +694,7 @@
         <v>44876</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -715,7 +714,7 @@
         <v>44877</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -747,15 +746,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7246309C-D378-4022-87E1-7F1AA2010793}">
   <dimension ref="A3:D7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="15.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
@@ -763,7 +762,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
@@ -777,41 +776,39 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5">
         <v>1</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4">
+      <c r="D5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4">
+      <c r="C6">
         <v>3</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7">
         <v>1</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7">
         <v>3</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7">
         <v>4</v>
       </c>
     </row>
@@ -823,13 +820,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCBA3D47-18D1-4B77-9A9E-1A4D57352B8B}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
@@ -837,7 +834,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -845,27 +842,27 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5">
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6">
         <v>44</v>
       </c>
     </row>
